--- a/artfynd/A 57804-2024 artfynd.xlsx
+++ b/artfynd/A 57804-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>319579</v>
+        <v>235557</v>
       </c>
       <c r="B2" t="n">
-        <v>89387</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445668.7393074308</v>
+        <v>445633</v>
       </c>
       <c r="R2" t="n">
-        <v>6943299.6858983</v>
+        <v>6943385</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,6 +765,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>235557</v>
+        <v>235558</v>
       </c>
       <c r="B3" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,12 +811,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445632.7944313397</v>
+        <v>445639</v>
       </c>
       <c r="R3" t="n">
-        <v>6943384.988831141</v>
+        <v>6943499</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +859,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>321861</v>
+        <v>321859</v>
       </c>
       <c r="B4" t="n">
-        <v>77587</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,26 +935,17 @@
           <t>(Lynge) Ahti</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Landaråsen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445648.3524767294</v>
+        <v>445669</v>
       </c>
       <c r="R4" t="n">
-        <v>6943433.994744361</v>
+        <v>6943300</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,19 +975,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1070,12 +1021,7 @@
         <v>321860</v>
       </c>
       <c r="B5" t="n">
-        <v>77587</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445632.7944313397</v>
+        <v>445633</v>
       </c>
       <c r="R5" t="n">
-        <v>6943384.988831141</v>
+        <v>6943385</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1149,19 +1095,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1202,15 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>319580</v>
+        <v>321861</v>
       </c>
       <c r="B6" t="n">
-        <v>89387</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,34 +1149,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Landaråsen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445638.3480735789</v>
+        <v>445648</v>
       </c>
       <c r="R6" t="n">
-        <v>6943358.194901221</v>
+        <v>6943434</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1275,19 +1215,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1328,15 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>403378</v>
+        <v>321862</v>
       </c>
       <c r="B7" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,34 +1269,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Landaråsen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445632.7944313397</v>
+        <v>445639</v>
       </c>
       <c r="R7" t="n">
-        <v>6943384.988831141</v>
+        <v>6943499</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1401,19 +1335,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,15 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>403379</v>
+        <v>321863</v>
       </c>
       <c r="B8" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,26 +1389,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1503,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445648.3524767294</v>
+        <v>445636</v>
       </c>
       <c r="R8" t="n">
-        <v>6943433.994744361</v>
+        <v>6943570</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1536,19 +1455,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1589,15 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>321863</v>
+        <v>322033</v>
       </c>
       <c r="B9" t="n">
-        <v>77587</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,26 +1526,17 @@
           <t>(Lynge) Ahti</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Landaråsen, Hjd</t>
+          <t>Landaråsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445636.2937829448</v>
+        <v>445750</v>
       </c>
       <c r="R9" t="n">
-        <v>6943570.00303</v>
+        <v>6943788</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1658,7 +1553,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1671,19 +1566,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1724,15 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>235558</v>
+        <v>319578</v>
       </c>
       <c r="B10" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,21 +1620,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1764,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445639.2779785949</v>
+        <v>445676</v>
       </c>
       <c r="R10" t="n">
-        <v>6943499.057144166</v>
+        <v>6943179</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1797,21 +1677,11 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1829,11 +1699,6 @@
       <c r="AI10" t="inlineStr">
         <is>
           <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1855,15 +1720,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>319578</v>
+        <v>319579</v>
       </c>
       <c r="B11" t="n">
-        <v>89387</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445675.5258952771</v>
+        <v>445669</v>
       </c>
       <c r="R11" t="n">
-        <v>6943179.407510717</v>
+        <v>6943300</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1928,19 +1788,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,15 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>321859</v>
+        <v>319580</v>
       </c>
       <c r="B12" t="n">
-        <v>77587</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1997,21 +1842,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2021,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445668.7393074308</v>
+        <v>445638</v>
       </c>
       <c r="R12" t="n">
-        <v>6943299.6858983</v>
+        <v>6943358</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2054,19 +1899,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2107,59 +1942,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>321862</v>
+        <v>350105</v>
       </c>
       <c r="B13" t="n">
-        <v>77587</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Landaråsen, Hjd</t>
+          <t>Landaråsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445639.2779785949</v>
+        <v>445609</v>
       </c>
       <c r="R13" t="n">
-        <v>6943499.057144166</v>
+        <v>6943697</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2176,7 +1997,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Härjedalen</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2189,19 +2010,9 @@
           <t>2008-09-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2008-09-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2242,15 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89592889</v>
+        <v>403378</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2258,37 +2064,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvällshögen, Jmt</t>
+          <t>Landaråsen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446622.9403642032</v>
+        <v>445633</v>
       </c>
       <c r="R14" t="n">
-        <v>6943574.203112192</v>
+        <v>6943385</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2302,7 +2108,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2312,22 +2118,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2338,35 +2134,40 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Olli Manninen, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89584416</v>
+        <v>403379</v>
       </c>
       <c r="B15" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2374,37 +2175,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvällshögen, Jmt</t>
+          <t>Landaråsen, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446638.8120419287</v>
+        <v>445648</v>
       </c>
       <c r="R15" t="n">
-        <v>6943557.834637453</v>
+        <v>6943434</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2418,7 +2228,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Härjedalen</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2428,22 +2238,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2454,57 +2254,62 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Olli Manninen, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Naturskyddare</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89592875</v>
+        <v>89592868</v>
       </c>
       <c r="B16" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>48</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2514,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446484.8934912919</v>
+        <v>446525</v>
       </c>
       <c r="R16" t="n">
-        <v>6943476.072054776</v>
+        <v>6943473</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2547,21 +2352,11 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2570,6 +2365,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Granlåga barklös</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2590,15 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89592906</v>
+        <v>89584430</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,21 +2401,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2630,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446533.8984697206</v>
+        <v>446632</v>
       </c>
       <c r="R17" t="n">
-        <v>6943513.03061045</v>
+        <v>6943615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2663,24 +2458,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2711,15 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89592863</v>
+        <v>89592857</v>
       </c>
       <c r="B18" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,21 +2502,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2751,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446511.8269942813</v>
+        <v>446511</v>
       </c>
       <c r="R18" t="n">
-        <v>6943488.066827028</v>
+        <v>6943520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2784,19 +2559,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2827,15 +2592,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89592877</v>
+        <v>89592896</v>
       </c>
       <c r="B19" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2843,21 +2603,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2867,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446619.0001098676</v>
+        <v>446509</v>
       </c>
       <c r="R19" t="n">
-        <v>6943587.156669676</v>
+        <v>6943514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2900,19 +2660,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2943,15 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89592859</v>
+        <v>89584424</v>
       </c>
       <c r="B20" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,21 +2704,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2983,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446474.0470133348</v>
+        <v>446636</v>
       </c>
       <c r="R20" t="n">
-        <v>6943461.055059851</v>
+        <v>6943602</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3016,19 +2761,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3059,15 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89592902</v>
+        <v>89592861</v>
       </c>
       <c r="B21" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3075,21 +2805,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3099,10 +2829,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446485.0571730539</v>
+        <v>446528</v>
       </c>
       <c r="R21" t="n">
-        <v>6943486.197601811</v>
+        <v>6943514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3132,19 +2862,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,12 +2898,7 @@
         <v>89592890</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3200,12 +2915,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3215,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446603.9248834525</v>
+        <v>446604</v>
       </c>
       <c r="R22" t="n">
-        <v>6943567.144024898</v>
+        <v>6943567</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3248,19 +2963,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3291,15 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89592878</v>
+        <v>89592901</v>
       </c>
       <c r="B23" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3307,21 +3007,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3331,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446603.0847519346</v>
+        <v>446530</v>
       </c>
       <c r="R23" t="n">
-        <v>6943572.221531074</v>
+        <v>6943520</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3364,19 +3064,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3407,15 +3097,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89592901</v>
+        <v>89584416</v>
       </c>
       <c r="B24" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3423,21 +3108,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3447,10 +3132,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446529.861843678</v>
+        <v>446639</v>
       </c>
       <c r="R24" t="n">
-        <v>6943520.001316114</v>
+        <v>6943558</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3480,19 +3165,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3523,15 +3198,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89592870</v>
+        <v>89584417</v>
       </c>
       <c r="B25" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3539,21 +3209,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3563,10 +3233,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446474.8869793658</v>
+        <v>446630</v>
       </c>
       <c r="R25" t="n">
-        <v>6943455.977347502</v>
+        <v>6943568</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3596,19 +3266,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3639,15 +3299,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89584421</v>
+        <v>89584422</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3655,21 +3310,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3679,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446631.0946365674</v>
+        <v>446634</v>
       </c>
       <c r="R26" t="n">
-        <v>6943593.867010532</v>
+        <v>6943599</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3712,19 +3367,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3755,15 +3400,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89592871</v>
+        <v>89592859</v>
       </c>
       <c r="B27" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3771,21 +3411,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3795,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446475.7939202245</v>
+        <v>446474</v>
       </c>
       <c r="R27" t="n">
-        <v>6943455.041932084</v>
+        <v>6943461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3828,19 +3468,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3871,15 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89592862</v>
+        <v>89592875</v>
       </c>
       <c r="B28" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3887,21 +3512,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1588</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3911,10 +3536,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446486.7817661363</v>
+        <v>446485</v>
       </c>
       <c r="R28" t="n">
-        <v>6943478.803768421</v>
+        <v>6943476</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3944,19 +3569,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3987,15 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89592896</v>
+        <v>89592886</v>
       </c>
       <c r="B29" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4003,21 +3613,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4027,10 +3637,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446509.0171029519</v>
+        <v>446476</v>
       </c>
       <c r="R29" t="n">
-        <v>6943513.892921916</v>
+        <v>6943458</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4060,19 +3670,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4103,15 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89592857</v>
+        <v>89592892</v>
       </c>
       <c r="B30" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4119,21 +3714,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4143,10 +3738,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446510.9573921472</v>
+        <v>446504</v>
       </c>
       <c r="R30" t="n">
-        <v>6943519.84634621</v>
+        <v>6943487</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4176,19 +3771,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4219,15 +3804,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>89592886</v>
+        <v>89592894</v>
       </c>
       <c r="B31" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4259,10 +3839,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>446475.838568255</v>
+        <v>446564</v>
       </c>
       <c r="R31" t="n">
-        <v>6943457.8034655</v>
+        <v>6943518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4292,19 +3872,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4335,15 +3905,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>89592867</v>
+        <v>89592897</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4351,21 +3916,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4375,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>446475.7790375418</v>
+        <v>446643</v>
       </c>
       <c r="R32" t="n">
-        <v>6943454.121420435</v>
+        <v>6943615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4408,24 +3973,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4456,15 +4006,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89592908</v>
+        <v>89592902</v>
       </c>
       <c r="B33" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4472,21 +4017,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4496,10 +4041,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446535.8238482938</v>
+        <v>446485</v>
       </c>
       <c r="R33" t="n">
-        <v>6943518.063556113</v>
+        <v>6943486</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4529,19 +4074,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4572,15 +4107,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>89584413</v>
+        <v>89592878</v>
       </c>
       <c r="B34" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4588,21 +4118,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4612,10 +4142,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446606.8697412127</v>
+        <v>446603</v>
       </c>
       <c r="R34" t="n">
-        <v>6943521.060219578</v>
+        <v>6943572</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4645,19 +4175,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4688,37 +4208,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>89584420</v>
+        <v>89584421</v>
       </c>
       <c r="B35" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4728,10 +4243,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446632.038680634</v>
+        <v>446631</v>
       </c>
       <c r="R35" t="n">
-        <v>6943595.232858823</v>
+        <v>6943594</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4761,19 +4276,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4804,19 +4309,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>89592884</v>
+        <v>89584426</v>
       </c>
       <c r="B36" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4844,10 +4344,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446472.1066250622</v>
+        <v>446636</v>
       </c>
       <c r="R36" t="n">
-        <v>6943455.10154973</v>
+        <v>6943602</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4877,19 +4377,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4920,37 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>89592861</v>
+        <v>89584429</v>
       </c>
       <c r="B37" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4960,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446527.9215887815</v>
+        <v>446630</v>
       </c>
       <c r="R37" t="n">
-        <v>6943514.047881722</v>
+        <v>6943613</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4993,19 +4478,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5036,37 +4511,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>89592888</v>
+        <v>89592884</v>
       </c>
       <c r="B38" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5076,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446598.8030550389</v>
+        <v>446472</v>
       </c>
       <c r="R38" t="n">
-        <v>6943564.00412222</v>
+        <v>6943455</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5109,19 +4579,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5152,15 +4612,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>89592892</v>
+        <v>89584410</v>
       </c>
       <c r="B39" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5168,21 +4623,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5192,10 +4647,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446503.9692583312</v>
+        <v>446557</v>
       </c>
       <c r="R39" t="n">
-        <v>6943486.812680758</v>
+        <v>6943510</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5225,19 +4680,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5268,15 +4713,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89584417</v>
+        <v>89584413</v>
       </c>
       <c r="B40" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5284,21 +4724,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5308,10 +4748,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>446630.2182286463</v>
+        <v>446607</v>
       </c>
       <c r="R40" t="n">
-        <v>6943568.10110133</v>
+        <v>6943521</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5341,19 +4781,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5384,37 +4814,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89592868</v>
+        <v>89592871</v>
       </c>
       <c r="B41" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>48</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5424,10 +4849,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446524.9554015272</v>
+        <v>446476</v>
       </c>
       <c r="R41" t="n">
-        <v>6943473.122821882</v>
+        <v>6943455</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5457,21 +4882,11 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5480,11 +4895,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Granlåga barklös</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5505,37 +4915,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>89592864</v>
+        <v>89592873</v>
       </c>
       <c r="B42" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>105930</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5545,10 +4950,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446488.0528972759</v>
+        <v>446545</v>
       </c>
       <c r="R42" t="n">
-        <v>6943471.877623296</v>
+        <v>6943535</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5578,19 +4983,9 @@
           <t>2020-08-26</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2020-08-26</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5614,6 +5009,1127 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>89592877</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>446619</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6943587</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>89592888</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>446599</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6943564</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>89592862</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92097</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>446487</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6943479</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>89584420</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>446632</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6943595</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>89592889</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>446623</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6943574</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>89592898</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>446561</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6943604</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>89592870</v>
+      </c>
+      <c r="B49" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>446475</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6943456</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>89592887</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>446561</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6943604</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>89592867</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>446476</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6943454</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>89592906</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>446534</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6943513</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>89592864</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kvällshögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>446488</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6943472</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 57804-2024 artfynd.xlsx
+++ b/artfynd/A 57804-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/235557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/235558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/321859</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/321860</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/321861</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1375,6 +1405,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/321862</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/321863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1606,6 +1646,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/322033</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1717,6 +1762,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/319578</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1828,6 +1878,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/319579</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1939,6 +1994,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/319580</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/350105</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/403378</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2281,6 +2351,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/403379</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2387,6 +2462,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592868</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584430</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2589,6 +2674,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592857</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2690,6 +2780,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592896</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2791,6 +2886,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584424</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592861</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2993,6 +3098,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592890</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3094,6 +3204,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592901</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3195,6 +3310,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584416</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3296,6 +3416,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584417</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3397,6 +3522,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584422</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3498,6 +3628,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592859</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3599,6 +3734,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592875</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3700,6 +3840,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592886</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3801,6 +3946,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592892</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3902,6 +4052,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592894</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4003,6 +4158,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592897</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4104,6 +4264,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592902</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4205,6 +4370,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592878</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4306,6 +4476,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584421</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4407,6 +4582,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584426</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4508,6 +4688,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584429</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4609,6 +4794,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592884</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4710,6 +4900,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584410</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4811,6 +5006,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584413</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4912,6 +5112,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592871</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5013,6 +5218,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592873</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5114,6 +5324,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592877</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5215,6 +5430,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592888</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5316,6 +5536,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592862</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5417,6 +5642,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89584420</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5518,6 +5748,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592889</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5619,6 +5854,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592898</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5720,6 +5960,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592870</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5821,6 +6066,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592887</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5927,6 +6177,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592867</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6033,6 +6288,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592906</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6134,8 +6394,67 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89592864</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>